--- a/output/pdf_financials_xlsx/NSJ.xlsx
+++ b/output/pdf_financials_xlsx/NSJ.xlsx
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.390357</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.390357</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.390357</v>
       </c>
     </row>
     <row r="93">
@@ -3048,7 +3048,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3391,7 +3395,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>0.390357</v>
       </c>

--- a/output/pdf_financials_xlsx/NSJ.xlsx
+++ b/output/pdf_financials_xlsx/NSJ.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.246511</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.09315</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.052514</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.246511</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.09315</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.052514</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.260129</v>
+        <v>0.013618</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.094268</v>
+        <v>0.001118</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.052514</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/NSJ.xlsx
+++ b/output/pdf_financials_xlsx/NSJ.xlsx
@@ -2069,13 +2069,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.026807</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.005307</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.006249</v>
       </c>
     </row>
     <row r="102">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.024825</v>
+        <v>0.051632</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.120064</v>
+        <v>0.125371</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.249208</v>
+        <v>0.255457</v>
       </c>
     </row>
     <row r="107">
@@ -3490,7 +3490,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
         <v>0.026807</v>
       </c>
